--- a/data/credit_bond_2026-09-21.xlsx
+++ b/data/credit_bond_2026-09-21.xlsx
@@ -959,7 +959,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9900/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-21.xlsx
+++ b/data/credit_bond_2026-09-21.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-21" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-22" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-21</t>
+          <t>数据来源：DM    2026-09-22</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,11 @@
           <t>09-21 17:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>212680052.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -709,10 +713,16 @@
       <c r="E3" s="4" t="n">
         <v>50.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>50.0</v>
+      </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>27.3</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -720,7 +730,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25中信银行科创债(柜台)</t>
+          <t>25中信银行科创债</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -735,7 +745,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4875</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -745,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A+ 84.44</t>
+          <t>A+ 84.81</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -913,7 +923,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-21 17:00</t>
+          <t>09-21 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-21.xlsx
+++ b/data/credit_bond_2026-09-21.xlsx
@@ -945,8 +945,12 @@
           <t>1.80 ~ 2.30</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>31.71</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.96</t>
@@ -969,7 +973,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.9900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-21.xlsx
+++ b/data/credit_bond_2026-09-21.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-22" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-23" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-22</t>
+          <t>数据来源：DM    2026-09-23</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A+ 84.81</t>
+          <t>A+ 83.58</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9900/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-21.xlsx
+++ b/data/credit_bond_2026-09-21.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-23" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-24" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A+ 83.58</t>
+          <t>A+ 82.60</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -939,7 +939,9 @@
       <c r="E4" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.30</t>
@@ -983,7 +985,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 13.17</t>
+          <t>C- 11.29</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1006,7 +1008,9 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-09-21.xlsx
+++ b/data/credit_bond_2026-09-21.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-24" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-25" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A+ 82.60</t>
+          <t>A+ 84.43</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -1077,75 +1077,313 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-23</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AZ4" s="3"/>
+    </row>
+    <row r="5" customHeight="true" ht="18.0">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>26畅途租赁PPN003</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>09-21 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>032680534.IB</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2.50 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>26畅途租赁PPN002</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2.59Y</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2.3331</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>上海畅途融资租赁有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>D+ 9.58</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>09-21 09:00</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>1.2133</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>2.73%~2.83%</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>上海畅途融资租赁有限公司2026年度第三期定向债务融资工具采用动态调整方式发行，发行基础规模2亿元，发行金额上限3亿元，用于偿还发行人本部金融机构借款，穿透用于3,454笔汽车融资租赁项目的投放。</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>平安银行股份有限公司,广东顺德农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>中外合资企业</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>上海畅途融资租赁有限公司2026年度第三期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-22</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-23</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
+      <c r="AV5" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AY4" s="3" t="inlineStr">
+      <c r="AY5" s="3" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ5" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
